--- a/docs/special_rules_review_matrix.xlsx
+++ b/docs/special_rules_review_matrix.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U517"/>
+  <dimension ref="A1:V517"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,6 +534,11 @@
           <t>Grant Target</t>
         </is>
       </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -607,6 +612,11 @@
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -680,6 +690,11 @@
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -753,6 +768,11 @@
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -826,6 +846,11 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -899,6 +924,11 @@
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -972,6 +1002,11 @@
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1045,6 +1080,11 @@
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1118,6 +1158,11 @@
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1191,6 +1236,11 @@
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1264,6 +1314,11 @@
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1333,6 +1388,11 @@
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1402,6 +1462,11 @@
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1475,6 +1540,11 @@
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1548,6 +1618,11 @@
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1621,6 +1696,11 @@
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1694,6 +1774,11 @@
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1767,6 +1852,11 @@
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1840,6 +1930,11 @@
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1909,6 +2004,11 @@
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1978,6 +2078,11 @@
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2051,6 +2156,11 @@
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2124,6 +2234,11 @@
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2193,6 +2308,11 @@
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2262,6 +2382,11 @@
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2331,6 +2456,11 @@
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2400,6 +2530,11 @@
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2473,6 +2608,11 @@
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2546,6 +2686,11 @@
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2615,6 +2760,11 @@
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2688,6 +2838,11 @@
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2761,6 +2916,11 @@
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2830,6 +2990,11 @@
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2899,6 +3064,11 @@
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2968,6 +3138,11 @@
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3041,6 +3216,11 @@
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3110,6 +3290,11 @@
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3183,6 +3368,11 @@
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3256,6 +3446,11 @@
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3329,6 +3524,11 @@
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3402,6 +3602,11 @@
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3475,6 +3680,11 @@
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3548,6 +3758,11 @@
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3621,6 +3836,11 @@
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3694,6 +3914,11 @@
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3763,6 +3988,11 @@
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3832,6 +4062,11 @@
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3901,6 +4136,11 @@
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr"/>
       <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3974,6 +4214,11 @@
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4047,6 +4292,11 @@
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4120,6 +4370,11 @@
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4193,6 +4448,11 @@
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr"/>
       <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4266,6 +4526,11 @@
       <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr"/>
       <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4335,6 +4600,11 @@
       <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr"/>
       <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4404,6 +4674,11 @@
       <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr"/>
       <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4473,6 +4748,11 @@
       <c r="S56" t="inlineStr"/>
       <c r="T56" t="inlineStr"/>
       <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4542,6 +4822,11 @@
       <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr"/>
       <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4615,6 +4900,11 @@
       <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr"/>
       <c r="U58" t="inlineStr"/>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4684,6 +4974,11 @@
       <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr"/>
       <c r="U59" t="inlineStr"/>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4749,6 +5044,11 @@
       <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr"/>
       <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4820,6 +5120,11 @@
       <c r="U61" t="inlineStr">
         <is>
           <t>ENEMY_UNIT</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -4903,6 +5208,11 @@
           <t>SELF_UNIT</t>
         </is>
       </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4972,6 +5282,11 @@
       <c r="S63" t="inlineStr"/>
       <c r="T63" t="inlineStr"/>
       <c r="U63" t="inlineStr"/>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5049,6 +5364,11 @@
       <c r="S64" t="inlineStr"/>
       <c r="T64" t="inlineStr"/>
       <c r="U64" t="inlineStr"/>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -5110,6 +5430,11 @@
       <c r="S65" t="inlineStr"/>
       <c r="T65" t="inlineStr"/>
       <c r="U65" t="inlineStr"/>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5181,6 +5506,11 @@
       <c r="U66" t="inlineStr">
         <is>
           <t>FRIENDLY_UNIT</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -5254,6 +5584,11 @@
       <c r="U67" t="inlineStr">
         <is>
           <t>FRIENDLY_UNIT</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -5321,6 +5656,11 @@
       <c r="S68" t="inlineStr"/>
       <c r="T68" t="inlineStr"/>
       <c r="U68" t="inlineStr"/>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -5394,6 +5734,11 @@
           <t>FRIENDLY_UNIT</t>
         </is>
       </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -5465,6 +5810,11 @@
       <c r="U70" t="inlineStr">
         <is>
           <t>FRIENDLY_UNIT</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -5528,6 +5878,11 @@
       <c r="S71" t="inlineStr"/>
       <c r="T71" t="inlineStr"/>
       <c r="U71" t="inlineStr"/>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -5601,6 +5956,11 @@
           <t>ENEMY_UNIT</t>
         </is>
       </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -5674,6 +6034,11 @@
           <t>ENEMY_UNIT</t>
         </is>
       </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -5739,6 +6104,11 @@
           <t>SELF_UNIT</t>
         </is>
       </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5816,6 +6186,11 @@
           <t>FRIENDLY_UNIT</t>
         </is>
       </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5879,6 +6254,11 @@
       <c r="U76" t="inlineStr">
         <is>
           <t>SELF_UNIT</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -5950,6 +6330,11 @@
       <c r="S77" t="inlineStr"/>
       <c r="T77" t="inlineStr"/>
       <c r="U77" t="inlineStr"/>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -6019,6 +6404,11 @@
       <c r="S78" t="inlineStr"/>
       <c r="T78" t="inlineStr"/>
       <c r="U78" t="inlineStr"/>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -6086,6 +6476,11 @@
       <c r="U79" t="inlineStr">
         <is>
           <t>FRIENDLY_UNIT</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -6153,6 +6548,11 @@
       <c r="S80" t="inlineStr"/>
       <c r="T80" t="inlineStr"/>
       <c r="U80" t="inlineStr"/>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -6224,6 +6624,11 @@
       <c r="U81" t="inlineStr">
         <is>
           <t>FRIENDLY_UNIT</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -6291,6 +6696,11 @@
       <c r="S82" t="inlineStr"/>
       <c r="T82" t="inlineStr"/>
       <c r="U82" t="inlineStr"/>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -6356,6 +6766,11 @@
       <c r="S83" t="inlineStr"/>
       <c r="T83" t="inlineStr"/>
       <c r="U83" t="inlineStr"/>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -6427,6 +6842,11 @@
       <c r="U84" t="inlineStr">
         <is>
           <t>FRIENDLY_UNIT</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -6500,6 +6920,11 @@
       <c r="U85" t="inlineStr">
         <is>
           <t>FRIENDLY_UNIT</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -6575,6 +7000,11 @@
           <t>FRIENDLY_UNIT</t>
         </is>
       </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -6646,6 +7076,11 @@
       <c r="U87" t="inlineStr">
         <is>
           <t>FRIENDLY_UNIT</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -6721,6 +7156,11 @@
           <t>FRIENDLY_UNIT</t>
         </is>
       </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -6792,6 +7232,11 @@
       <c r="U89" t="inlineStr">
         <is>
           <t>ENEMY_UNIT</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -6859,6 +7304,11 @@
       <c r="S90" t="inlineStr"/>
       <c r="T90" t="inlineStr"/>
       <c r="U90" t="inlineStr"/>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -6924,6 +7374,11 @@
       <c r="S91" t="inlineStr"/>
       <c r="T91" t="inlineStr"/>
       <c r="U91" t="inlineStr"/>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -6997,6 +7452,11 @@
       <c r="S92" t="inlineStr"/>
       <c r="T92" t="inlineStr"/>
       <c r="U92" t="inlineStr"/>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -7062,6 +7522,11 @@
       <c r="S93" t="inlineStr"/>
       <c r="T93" t="inlineStr"/>
       <c r="U93" t="inlineStr"/>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -7131,6 +7596,11 @@
       <c r="S94" t="inlineStr"/>
       <c r="T94" t="inlineStr"/>
       <c r="U94" t="inlineStr"/>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -7194,6 +7664,11 @@
       <c r="U95" t="inlineStr">
         <is>
           <t>SELF_UNIT</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -7261,6 +7736,11 @@
       <c r="S96" t="inlineStr"/>
       <c r="T96" t="inlineStr"/>
       <c r="U96" t="inlineStr"/>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -7330,6 +7810,11 @@
       <c r="S97" t="inlineStr"/>
       <c r="T97" t="inlineStr"/>
       <c r="U97" t="inlineStr"/>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -7403,6 +7888,11 @@
       <c r="S98" t="inlineStr"/>
       <c r="T98" t="inlineStr"/>
       <c r="U98" t="inlineStr"/>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -7468,6 +7958,11 @@
       <c r="S99" t="inlineStr"/>
       <c r="T99" t="inlineStr"/>
       <c r="U99" t="inlineStr"/>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -7533,6 +8028,11 @@
       <c r="S100" t="inlineStr"/>
       <c r="T100" t="inlineStr"/>
       <c r="U100" t="inlineStr"/>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -7604,6 +8104,11 @@
       <c r="U101" t="inlineStr">
         <is>
           <t>FRIENDLY_UNIT</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -7675,6 +8180,11 @@
       <c r="S102" t="inlineStr"/>
       <c r="T102" t="inlineStr"/>
       <c r="U102" t="inlineStr"/>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -7740,6 +8250,11 @@
       <c r="S103" t="inlineStr"/>
       <c r="T103" t="inlineStr"/>
       <c r="U103" t="inlineStr"/>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -7813,6 +8328,11 @@
           <t>ENEMY_UNIT</t>
         </is>
       </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -7886,6 +8406,11 @@
           <t>FRIENDLY_UNIT</t>
         </is>
       </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -7959,6 +8484,11 @@
       <c r="S106" t="inlineStr"/>
       <c r="T106" t="inlineStr"/>
       <c r="U106" t="inlineStr"/>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -8032,6 +8562,11 @@
           <t>ENEMY_UNIT</t>
         </is>
       </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -8093,6 +8628,11 @@
       <c r="S108" t="inlineStr"/>
       <c r="T108" t="inlineStr"/>
       <c r="U108" t="inlineStr"/>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -8154,6 +8694,11 @@
       <c r="S109" t="inlineStr"/>
       <c r="T109" t="inlineStr"/>
       <c r="U109" t="inlineStr"/>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -8227,6 +8772,11 @@
           <t>ENEMY_UNIT</t>
         </is>
       </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -8298,6 +8848,11 @@
       <c r="U111" t="inlineStr">
         <is>
           <t>FRIENDLY_UNIT</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -8365,6 +8920,11 @@
       <c r="S112" t="inlineStr"/>
       <c r="T112" t="inlineStr"/>
       <c r="U112" t="inlineStr"/>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -8438,6 +8998,11 @@
           <t>FRIENDLY_UNIT</t>
         </is>
       </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -8507,6 +9072,11 @@
       <c r="S114" t="inlineStr"/>
       <c r="T114" t="inlineStr"/>
       <c r="U114" t="inlineStr"/>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -8588,6 +9158,11 @@
           <t>SELF</t>
         </is>
       </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -8657,6 +9232,11 @@
           <t>SELF_UNIT</t>
         </is>
       </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -8730,6 +9310,11 @@
       <c r="S117" t="inlineStr"/>
       <c r="T117" t="inlineStr"/>
       <c r="U117" t="inlineStr"/>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -8793,6 +9378,11 @@
       <c r="U118" t="inlineStr">
         <is>
           <t>SELF_UNIT</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -8860,6 +9450,11 @@
       <c r="S119" t="inlineStr"/>
       <c r="T119" t="inlineStr"/>
       <c r="U119" t="inlineStr"/>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -8933,6 +9528,11 @@
           <t>ENEMY_UNIT</t>
         </is>
       </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -8986,6 +9586,11 @@
       <c r="S121" t="inlineStr"/>
       <c r="T121" t="inlineStr"/>
       <c r="U121" t="inlineStr"/>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -9055,6 +9660,11 @@
       <c r="S122" t="inlineStr"/>
       <c r="T122" t="inlineStr"/>
       <c r="U122" t="inlineStr"/>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -9124,6 +9734,11 @@
       <c r="S123" t="inlineStr"/>
       <c r="T123" t="inlineStr"/>
       <c r="U123" t="inlineStr"/>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -9177,6 +9792,11 @@
       <c r="S124" t="inlineStr"/>
       <c r="T124" t="inlineStr"/>
       <c r="U124" t="inlineStr"/>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -9242,6 +9862,11 @@
           <t>SELF_UNIT</t>
         </is>
       </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -9323,6 +9948,11 @@
           <t>SELF_UNIT</t>
         </is>
       </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -9396,6 +10026,11 @@
       <c r="S127" t="inlineStr"/>
       <c r="T127" t="inlineStr"/>
       <c r="U127" t="inlineStr"/>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -9469,6 +10104,11 @@
       <c r="S128" t="inlineStr"/>
       <c r="T128" t="inlineStr"/>
       <c r="U128" t="inlineStr"/>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -9534,6 +10174,11 @@
       <c r="S129" t="inlineStr"/>
       <c r="T129" t="inlineStr"/>
       <c r="U129" t="inlineStr"/>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -9605,6 +10250,11 @@
       <c r="U130" t="inlineStr">
         <is>
           <t>ENEMY_UNIT</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -9676,6 +10326,11 @@
       <c r="S131" t="inlineStr"/>
       <c r="T131" t="inlineStr"/>
       <c r="U131" t="inlineStr"/>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -9745,6 +10400,11 @@
       <c r="S132" t="inlineStr"/>
       <c r="T132" t="inlineStr"/>
       <c r="U132" t="inlineStr"/>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -9814,6 +10474,11 @@
       <c r="S133" t="inlineStr"/>
       <c r="T133" t="inlineStr"/>
       <c r="U133" t="inlineStr"/>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -9883,6 +10548,11 @@
       <c r="S134" t="inlineStr"/>
       <c r="T134" t="inlineStr"/>
       <c r="U134" t="inlineStr"/>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -9948,6 +10618,11 @@
       <c r="S135" t="inlineStr"/>
       <c r="T135" t="inlineStr"/>
       <c r="U135" t="inlineStr"/>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -10009,6 +10684,11 @@
       <c r="S136" t="inlineStr"/>
       <c r="T136" t="inlineStr"/>
       <c r="U136" t="inlineStr"/>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -10080,6 +10760,11 @@
       <c r="U137" t="inlineStr">
         <is>
           <t>FRIENDLY_UNIT</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -10143,6 +10828,11 @@
       <c r="S138" t="inlineStr"/>
       <c r="T138" t="inlineStr"/>
       <c r="U138" t="inlineStr"/>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -10214,6 +10904,11 @@
       <c r="U139" t="inlineStr">
         <is>
           <t>FRIENDLY_UNIT</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -10289,6 +10984,11 @@
           <t>FRIENDLY_UNIT</t>
         </is>
       </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -10360,6 +11060,11 @@
       <c r="U141" t="inlineStr">
         <is>
           <t>ENEMY_UNIT</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -10427,6 +11132,11 @@
       <c r="S142" t="inlineStr"/>
       <c r="T142" t="inlineStr"/>
       <c r="U142" t="inlineStr"/>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -10492,6 +11202,11 @@
       <c r="S143" t="inlineStr"/>
       <c r="T143" t="inlineStr"/>
       <c r="U143" t="inlineStr"/>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -10569,6 +11284,11 @@
       <c r="S144" t="inlineStr"/>
       <c r="T144" t="inlineStr"/>
       <c r="U144" t="inlineStr"/>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -10634,6 +11354,11 @@
       <c r="S145" t="inlineStr"/>
       <c r="T145" t="inlineStr"/>
       <c r="U145" t="inlineStr"/>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -10699,6 +11424,11 @@
       <c r="S146" t="inlineStr"/>
       <c r="T146" t="inlineStr"/>
       <c r="U146" t="inlineStr"/>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -10760,6 +11490,11 @@
       <c r="S147" t="inlineStr"/>
       <c r="T147" t="inlineStr"/>
       <c r="U147" t="inlineStr"/>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -10825,6 +11560,11 @@
       <c r="S148" t="inlineStr"/>
       <c r="T148" t="inlineStr"/>
       <c r="U148" t="inlineStr"/>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -10898,6 +11638,11 @@
       <c r="S149" t="inlineStr"/>
       <c r="T149" t="inlineStr"/>
       <c r="U149" t="inlineStr"/>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -10963,6 +11708,11 @@
       <c r="S150" t="inlineStr"/>
       <c r="T150" t="inlineStr"/>
       <c r="U150" t="inlineStr"/>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -11032,6 +11782,11 @@
       <c r="S151" t="inlineStr"/>
       <c r="T151" t="inlineStr"/>
       <c r="U151" t="inlineStr"/>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -11101,6 +11856,11 @@
       <c r="S152" t="inlineStr"/>
       <c r="T152" t="inlineStr"/>
       <c r="U152" t="inlineStr"/>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -11166,6 +11926,11 @@
           <t>SELF_UNIT</t>
         </is>
       </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -11219,6 +11984,11 @@
       <c r="S154" t="inlineStr"/>
       <c r="T154" t="inlineStr"/>
       <c r="U154" t="inlineStr"/>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -11292,6 +12062,11 @@
       <c r="S155" t="inlineStr"/>
       <c r="T155" t="inlineStr"/>
       <c r="U155" t="inlineStr"/>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -11365,6 +12140,11 @@
       <c r="S156" t="inlineStr"/>
       <c r="T156" t="inlineStr"/>
       <c r="U156" t="inlineStr"/>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -11434,6 +12214,11 @@
       <c r="S157" t="inlineStr"/>
       <c r="T157" t="inlineStr"/>
       <c r="U157" t="inlineStr"/>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -11503,6 +12288,11 @@
       <c r="S158" t="inlineStr"/>
       <c r="T158" t="inlineStr"/>
       <c r="U158" t="inlineStr"/>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -11568,6 +12358,11 @@
       <c r="S159" t="inlineStr"/>
       <c r="T159" t="inlineStr"/>
       <c r="U159" t="inlineStr"/>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -11635,6 +12430,11 @@
       <c r="U160" t="inlineStr">
         <is>
           <t>SELF</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -11702,6 +12502,11 @@
           <t>SELF_UNIT</t>
         </is>
       </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -11763,6 +12568,11 @@
       <c r="S162" t="inlineStr"/>
       <c r="T162" t="inlineStr"/>
       <c r="U162" t="inlineStr"/>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -11836,6 +12646,11 @@
       <c r="S163" t="inlineStr"/>
       <c r="T163" t="inlineStr"/>
       <c r="U163" t="inlineStr"/>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -11901,6 +12716,11 @@
       <c r="S164" t="inlineStr"/>
       <c r="T164" t="inlineStr"/>
       <c r="U164" t="inlineStr"/>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -11966,6 +12786,11 @@
       <c r="S165" t="inlineStr"/>
       <c r="T165" t="inlineStr"/>
       <c r="U165" t="inlineStr"/>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -12031,6 +12856,11 @@
       <c r="S166" t="inlineStr"/>
       <c r="T166" t="inlineStr"/>
       <c r="U166" t="inlineStr"/>
+      <c r="V166" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -12102,6 +12932,11 @@
       <c r="U167" t="inlineStr">
         <is>
           <t>FRIENDLY_UNIT</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -12169,6 +13004,11 @@
       <c r="S168" t="inlineStr"/>
       <c r="T168" t="inlineStr"/>
       <c r="U168" t="inlineStr"/>
+      <c r="V168" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -12234,6 +13074,11 @@
       <c r="S169" t="inlineStr"/>
       <c r="T169" t="inlineStr"/>
       <c r="U169" t="inlineStr"/>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -12307,6 +13152,11 @@
           <t>FRIENDLY_UNIT</t>
         </is>
       </c>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -12378,6 +13228,11 @@
       <c r="U171" t="inlineStr">
         <is>
           <t>FRIENDLY_UNIT</t>
+        </is>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -12445,6 +13300,11 @@
       <c r="S172" t="inlineStr"/>
       <c r="T172" t="inlineStr"/>
       <c r="U172" t="inlineStr"/>
+      <c r="V172" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -12506,6 +13366,11 @@
       <c r="S173" t="inlineStr"/>
       <c r="T173" t="inlineStr"/>
       <c r="U173" t="inlineStr"/>
+      <c r="V173" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -12579,6 +13444,11 @@
       <c r="S174" t="inlineStr"/>
       <c r="T174" t="inlineStr"/>
       <c r="U174" t="inlineStr"/>
+      <c r="V174" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -12642,6 +13512,11 @@
       <c r="U175" t="inlineStr">
         <is>
           <t>SELF_UNIT</t>
+        </is>
+      </c>
+      <c r="V175" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -12709,6 +13584,11 @@
       <c r="S176" t="inlineStr"/>
       <c r="T176" t="inlineStr"/>
       <c r="U176" t="inlineStr"/>
+      <c r="V176" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -12762,6 +13642,11 @@
       <c r="S177" t="inlineStr"/>
       <c r="T177" t="inlineStr"/>
       <c r="U177" t="inlineStr"/>
+      <c r="V177" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -12833,6 +13718,11 @@
       <c r="U178" t="inlineStr">
         <is>
           <t>FRIENDLY_UNIT</t>
+        </is>
+      </c>
+      <c r="V178" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -12888,6 +13778,11 @@
       <c r="S179" t="inlineStr"/>
       <c r="T179" t="inlineStr"/>
       <c r="U179" t="inlineStr"/>
+      <c r="V179" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -12961,6 +13856,11 @@
       <c r="S180" t="inlineStr"/>
       <c r="T180" t="inlineStr"/>
       <c r="U180" t="inlineStr"/>
+      <c r="V180" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -13026,6 +13926,11 @@
       <c r="S181" t="inlineStr"/>
       <c r="T181" t="inlineStr"/>
       <c r="U181" t="inlineStr"/>
+      <c r="V181" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -13099,6 +14004,11 @@
           <t>FRIENDLY_UNIT</t>
         </is>
       </c>
+      <c r="V182" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -13164,6 +14074,11 @@
       <c r="S183" t="inlineStr"/>
       <c r="T183" t="inlineStr"/>
       <c r="U183" t="inlineStr"/>
+      <c r="V183" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -13243,6 +14158,11 @@
       <c r="U184" t="inlineStr">
         <is>
           <t>SELF_UNIT</t>
+        </is>
+      </c>
+      <c r="V184" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -13310,6 +14230,11 @@
       <c r="S185" t="inlineStr"/>
       <c r="T185" t="inlineStr"/>
       <c r="U185" t="inlineStr"/>
+      <c r="V185" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -13383,6 +14308,11 @@
       <c r="S186" t="inlineStr"/>
       <c r="T186" t="inlineStr"/>
       <c r="U186" t="inlineStr"/>
+      <c r="V186" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -13450,6 +14380,11 @@
       <c r="U187" t="inlineStr">
         <is>
           <t>SELF</t>
+        </is>
+      </c>
+      <c r="V187" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -13517,6 +14452,11 @@
           <t>SELF_UNIT</t>
         </is>
       </c>
+      <c r="V188" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -13588,6 +14528,11 @@
       <c r="U189" t="inlineStr">
         <is>
           <t>FRIENDLY_UNIT</t>
+        </is>
+      </c>
+      <c r="V189" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -13655,6 +14600,11 @@
       <c r="S190" t="inlineStr"/>
       <c r="T190" t="inlineStr"/>
       <c r="U190" t="inlineStr"/>
+      <c r="V190" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -13720,6 +14670,11 @@
       <c r="S191" t="inlineStr"/>
       <c r="T191" t="inlineStr"/>
       <c r="U191" t="inlineStr"/>
+      <c r="V191" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -13791,6 +14746,11 @@
       <c r="U192" t="inlineStr">
         <is>
           <t>FRIENDLY_UNIT</t>
+        </is>
+      </c>
+      <c r="V192" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -13858,6 +14818,11 @@
       <c r="S193" t="inlineStr"/>
       <c r="T193" t="inlineStr"/>
       <c r="U193" t="inlineStr"/>
+      <c r="V193" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -13931,6 +14896,11 @@
       <c r="S194" t="inlineStr"/>
       <c r="T194" t="inlineStr"/>
       <c r="U194" t="inlineStr"/>
+      <c r="V194" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -13996,6 +14966,11 @@
           <t>SELF_UNIT</t>
         </is>
       </c>
+      <c r="V195" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -14073,6 +15048,11 @@
       <c r="S196" t="inlineStr"/>
       <c r="T196" t="inlineStr"/>
       <c r="U196" t="inlineStr"/>
+      <c r="V196" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -14146,6 +15126,11 @@
       <c r="S197" t="inlineStr"/>
       <c r="T197" t="inlineStr"/>
       <c r="U197" t="inlineStr"/>
+      <c r="V197" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -14219,6 +15204,11 @@
       <c r="S198" t="inlineStr"/>
       <c r="T198" t="inlineStr"/>
       <c r="U198" t="inlineStr"/>
+      <c r="V198" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -14300,6 +15290,11 @@
           <t>SELF_UNIT</t>
         </is>
       </c>
+      <c r="V199" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -14371,6 +15366,11 @@
       <c r="U200" t="inlineStr">
         <is>
           <t>ENEMY_UNIT</t>
+        </is>
+      </c>
+      <c r="V200" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -14438,6 +15438,11 @@
       <c r="S201" t="inlineStr"/>
       <c r="T201" t="inlineStr"/>
       <c r="U201" t="inlineStr"/>
+      <c r="V201" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -14503,6 +15508,11 @@
       <c r="S202" t="inlineStr"/>
       <c r="T202" t="inlineStr"/>
       <c r="U202" t="inlineStr"/>
+      <c r="V202" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -14568,6 +15578,11 @@
           <t>SELF_UNIT</t>
         </is>
       </c>
+      <c r="V203" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -14633,6 +15648,11 @@
           <t>SELF_UNIT</t>
         </is>
       </c>
+      <c r="V204" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -14706,6 +15726,11 @@
       <c r="S205" t="inlineStr"/>
       <c r="T205" t="inlineStr"/>
       <c r="U205" t="inlineStr"/>
+      <c r="V205" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -14779,6 +15804,11 @@
           <t>FRIENDLY_UNIT</t>
         </is>
       </c>
+      <c r="V206" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -14848,6 +15878,11 @@
       <c r="S207" t="inlineStr"/>
       <c r="T207" t="inlineStr"/>
       <c r="U207" t="inlineStr"/>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -14923,6 +15958,11 @@
       <c r="U208" t="inlineStr">
         <is>
           <t>SELF</t>
+        </is>
+      </c>
+      <c r="V208" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -14990,6 +16030,11 @@
           <t>SELF_UNIT</t>
         </is>
       </c>
+      <c r="V209" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -15063,6 +16108,11 @@
           <t>FRIENDLY_UNIT</t>
         </is>
       </c>
+      <c r="V210" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -15128,6 +16178,11 @@
       <c r="S211" t="inlineStr"/>
       <c r="T211" t="inlineStr"/>
       <c r="U211" t="inlineStr"/>
+      <c r="V211" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -15193,6 +16248,11 @@
           <t>SELF_UNIT</t>
         </is>
       </c>
+      <c r="V212" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -15258,6 +16318,11 @@
       <c r="S213" t="inlineStr"/>
       <c r="T213" t="inlineStr"/>
       <c r="U213" t="inlineStr"/>
+      <c r="V213" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -15323,6 +16388,11 @@
           <t>SELF_UNIT</t>
         </is>
       </c>
+      <c r="V214" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -15394,6 +16464,11 @@
       <c r="U215" t="inlineStr">
         <is>
           <t>FRIENDLY_UNIT</t>
+        </is>
+      </c>
+      <c r="V215" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -15461,6 +16536,11 @@
       <c r="S216" t="inlineStr"/>
       <c r="T216" t="inlineStr"/>
       <c r="U216" t="inlineStr"/>
+      <c r="V216" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -15526,6 +16606,11 @@
       <c r="S217" t="inlineStr"/>
       <c r="T217" t="inlineStr"/>
       <c r="U217" t="inlineStr"/>
+      <c r="V217" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -15591,6 +16676,11 @@
       <c r="S218" t="inlineStr"/>
       <c r="T218" t="inlineStr"/>
       <c r="U218" t="inlineStr"/>
+      <c r="V218" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -15664,6 +16754,11 @@
       <c r="S219" t="inlineStr"/>
       <c r="T219" t="inlineStr"/>
       <c r="U219" t="inlineStr"/>
+      <c r="V219" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -15729,6 +16824,11 @@
           <t>SELF_UNIT</t>
         </is>
       </c>
+      <c r="V220" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -15802,6 +16902,11 @@
       <c r="S221" t="inlineStr"/>
       <c r="T221" t="inlineStr"/>
       <c r="U221" t="inlineStr"/>
+      <c r="V221" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -15873,6 +16978,11 @@
       <c r="U222" t="inlineStr">
         <is>
           <t>ENEMY_UNIT</t>
+        </is>
+      </c>
+      <c r="V222" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -15940,6 +17050,11 @@
       <c r="S223" t="inlineStr"/>
       <c r="T223" t="inlineStr"/>
       <c r="U223" t="inlineStr"/>
+      <c r="V223" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -16005,6 +17120,11 @@
       <c r="S224" t="inlineStr"/>
       <c r="T224" t="inlineStr"/>
       <c r="U224" t="inlineStr"/>
+      <c r="V224" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -16074,6 +17194,11 @@
       <c r="S225" t="inlineStr"/>
       <c r="T225" t="inlineStr"/>
       <c r="U225" t="inlineStr"/>
+      <c r="V225" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -16145,6 +17270,11 @@
       <c r="U226" t="inlineStr">
         <is>
           <t>FRIENDLY_UNIT</t>
+        </is>
+      </c>
+      <c r="V226" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -16220,6 +17350,11 @@
       <c r="S227" t="inlineStr"/>
       <c r="T227" t="inlineStr"/>
       <c r="U227" t="inlineStr"/>
+      <c r="V227" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -16285,6 +17420,11 @@
           <t>SELF_UNIT</t>
         </is>
       </c>
+      <c r="V228" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -16346,6 +17486,11 @@
       <c r="S229" t="inlineStr"/>
       <c r="T229" t="inlineStr"/>
       <c r="U229" t="inlineStr"/>
+      <c r="V229" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -16411,6 +17556,11 @@
           <t>SELF_UNIT</t>
         </is>
       </c>
+      <c r="V230" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -16472,6 +17622,11 @@
       <c r="S231" t="inlineStr"/>
       <c r="T231" t="inlineStr"/>
       <c r="U231" t="inlineStr"/>
+      <c r="V231" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -16535,6 +17690,11 @@
       <c r="U232" t="inlineStr">
         <is>
           <t>SELF_UNIT</t>
+        </is>
+      </c>
+      <c r="V232" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -16606,6 +17766,11 @@
       <c r="S233" t="inlineStr"/>
       <c r="T233" t="inlineStr"/>
       <c r="U233" t="inlineStr"/>
+      <c r="V233" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -16669,6 +17834,11 @@
       <c r="U234" t="inlineStr">
         <is>
           <t>SELF_UNIT</t>
+        </is>
+      </c>
+      <c r="V234" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -16736,6 +17906,11 @@
       <c r="S235" t="inlineStr"/>
       <c r="T235" t="inlineStr"/>
       <c r="U235" t="inlineStr"/>
+      <c r="V235" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -16805,6 +17980,11 @@
       <c r="S236" t="inlineStr"/>
       <c r="T236" t="inlineStr"/>
       <c r="U236" t="inlineStr"/>
+      <c r="V236" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -16868,6 +18048,11 @@
       <c r="U237" t="inlineStr">
         <is>
           <t>SELF_UNIT</t>
+        </is>
+      </c>
+      <c r="V237" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -16935,6 +18120,11 @@
       <c r="S238" t="inlineStr"/>
       <c r="T238" t="inlineStr"/>
       <c r="U238" t="inlineStr"/>
+      <c r="V238" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -17008,6 +18198,11 @@
           <t>FRIENDLY_UNIT</t>
         </is>
       </c>
+      <c r="V239" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -17065,6 +18260,11 @@
       <c r="S240" t="inlineStr"/>
       <c r="T240" t="inlineStr"/>
       <c r="U240" t="inlineStr"/>
+      <c r="V240" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -17146,6 +18346,11 @@
           <t>SELF_UNIT</t>
         </is>
       </c>
+      <c r="V241" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -17227,6 +18432,11 @@
           <t>SELF_UNIT</t>
         </is>
       </c>
+      <c r="V242" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -17296,6 +18506,11 @@
       <c r="S243" t="inlineStr"/>
       <c r="T243" t="inlineStr"/>
       <c r="U243" t="inlineStr"/>
+      <c r="V243" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -17349,6 +18564,11 @@
       <c r="S244" t="inlineStr"/>
       <c r="T244" t="inlineStr"/>
       <c r="U244" t="inlineStr"/>
+      <c r="V244" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -17410,6 +18630,11 @@
           <t>SELF_UNIT</t>
         </is>
       </c>
+      <c r="V245" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -17483,6 +18708,11 @@
           <t>FRIENDLY_UNIT</t>
         </is>
       </c>
+      <c r="V246" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -17548,6 +18778,11 @@
       <c r="S247" t="inlineStr"/>
       <c r="T247" t="inlineStr"/>
       <c r="U247" t="inlineStr"/>
+      <c r="V247" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -17621,6 +18856,11 @@
           <t>ENEMY_UNIT</t>
         </is>
       </c>
+      <c r="V248" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -17686,6 +18926,11 @@
           <t>SELF_UNIT</t>
         </is>
       </c>
+      <c r="V249" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -17743,6 +18988,11 @@
       <c r="S250" t="inlineStr"/>
       <c r="T250" t="inlineStr"/>
       <c r="U250" t="inlineStr"/>
+      <c r="V250" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -17808,6 +19058,11 @@
           <t>SELF_UNIT</t>
         </is>
       </c>
+      <c r="V251" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -17877,6 +19132,11 @@
       <c r="S252" t="inlineStr"/>
       <c r="T252" t="inlineStr"/>
       <c r="U252" t="inlineStr"/>
+      <c r="V252" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -17958,6 +19218,11 @@
           <t>SELF_UNIT</t>
         </is>
       </c>
+      <c r="V253" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -18031,6 +19296,11 @@
           <t>FRIENDLY_UNIT</t>
         </is>
       </c>
+      <c r="V254" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -18084,6 +19354,11 @@
       <c r="S255" t="inlineStr"/>
       <c r="T255" t="inlineStr"/>
       <c r="U255" t="inlineStr"/>
+      <c r="V255" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -18157,6 +19432,11 @@
           <t>FRIENDLY_UNIT</t>
         </is>
       </c>
+      <c r="V256" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -18230,6 +19510,11 @@
           <t>FRIENDLY_UNIT</t>
         </is>
       </c>
+      <c r="V257" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -18303,6 +19588,11 @@
       <c r="S258" t="inlineStr"/>
       <c r="T258" t="inlineStr"/>
       <c r="U258" t="inlineStr"/>
+      <c r="V258" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -18368,6 +19658,11 @@
       <c r="S259" t="inlineStr"/>
       <c r="T259" t="inlineStr"/>
       <c r="U259" t="inlineStr"/>
+      <c r="V259" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -18433,6 +19728,11 @@
       <c r="S260" t="inlineStr"/>
       <c r="T260" t="inlineStr"/>
       <c r="U260" t="inlineStr"/>
+      <c r="V260" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -18506,6 +19806,11 @@
           <t>FRIENDLY_UNIT</t>
         </is>
       </c>
+      <c r="V261" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -18577,6 +19882,11 @@
       <c r="U262" t="inlineStr">
         <is>
           <t>ENEMY_UNIT</t>
+        </is>
+      </c>
+      <c r="V262" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -18644,6 +19954,11 @@
       <c r="S263" t="inlineStr"/>
       <c r="T263" t="inlineStr"/>
       <c r="U263" t="inlineStr"/>
+      <c r="V263" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -18709,6 +20024,11 @@
       <c r="S264" t="inlineStr"/>
       <c r="T264" t="inlineStr"/>
       <c r="U264" t="inlineStr"/>
+      <c r="V264" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -18782,6 +20102,11 @@
       <c r="S265" t="inlineStr"/>
       <c r="T265" t="inlineStr"/>
       <c r="U265" t="inlineStr"/>
+      <c r="V265" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -18839,6 +20164,11 @@
       <c r="S266" t="inlineStr"/>
       <c r="T266" t="inlineStr"/>
       <c r="U266" t="inlineStr"/>
+      <c r="V266" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -18904,6 +20234,11 @@
       <c r="S267" t="inlineStr"/>
       <c r="T267" t="inlineStr"/>
       <c r="U267" t="inlineStr"/>
+      <c r="V267" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -18969,6 +20304,11 @@
       <c r="S268" t="inlineStr"/>
       <c r="T268" t="inlineStr"/>
       <c r="U268" t="inlineStr"/>
+      <c r="V268" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -19042,6 +20382,11 @@
           <t>FRIENDLY_UNIT</t>
         </is>
       </c>
+      <c r="V269" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -19115,6 +20460,11 @@
           <t>FRIENDLY_UNIT</t>
         </is>
       </c>
+      <c r="V270" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -19188,6 +20538,11 @@
       <c r="S271" t="inlineStr"/>
       <c r="T271" t="inlineStr"/>
       <c r="U271" t="inlineStr"/>
+      <c r="V271" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -19271,6 +20626,11 @@
       <c r="U272" t="inlineStr">
         <is>
           <t>SELF</t>
+        </is>
+      </c>
+      <c r="V272" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -19338,6 +20698,11 @@
           <t>SELF_UNIT</t>
         </is>
       </c>
+      <c r="V273" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -19407,6 +20772,11 @@
       <c r="S274" t="inlineStr"/>
       <c r="T274" t="inlineStr"/>
       <c r="U274" t="inlineStr"/>
+      <c r="V274" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -19472,6 +20842,11 @@
           <t>SELF_UNIT</t>
         </is>
       </c>
+      <c r="V275" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -19525,6 +20900,11 @@
       <c r="S276" t="inlineStr"/>
       <c r="T276" t="inlineStr"/>
       <c r="U276" t="inlineStr"/>
+      <c r="V276" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -19590,6 +20970,11 @@
           <t>SELF_UNIT</t>
         </is>
       </c>
+      <c r="V277" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -19655,6 +21040,11 @@
           <t>SELF_UNIT</t>
         </is>
       </c>
+      <c r="V278" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -19724,6 +21114,11 @@
       <c r="S279" t="inlineStr"/>
       <c r="T279" t="inlineStr"/>
       <c r="U279" t="inlineStr"/>
+      <c r="V279" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -19789,6 +21184,11 @@
           <t>SELF_UNIT</t>
         </is>
       </c>
+      <c r="V280" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -19854,6 +21254,11 @@
       <c r="S281" t="inlineStr"/>
       <c r="T281" t="inlineStr"/>
       <c r="U281" t="inlineStr"/>
+      <c r="V281" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -19925,6 +21330,11 @@
       <c r="U282" t="inlineStr">
         <is>
           <t>FRIENDLY_UNIT</t>
+        </is>
+      </c>
+      <c r="V282" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -19992,6 +21402,11 @@
       <c r="S283" t="inlineStr"/>
       <c r="T283" t="inlineStr"/>
       <c r="U283" t="inlineStr"/>
+      <c r="V283" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -20061,6 +21476,11 @@
       <c r="S284" t="inlineStr"/>
       <c r="T284" t="inlineStr"/>
       <c r="U284" t="inlineStr"/>
+      <c r="V284" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -20126,6 +21546,11 @@
       <c r="S285" t="inlineStr"/>
       <c r="T285" t="inlineStr"/>
       <c r="U285" t="inlineStr"/>
+      <c r="V285" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -20191,6 +21616,11 @@
       <c r="S286" t="inlineStr"/>
       <c r="T286" t="inlineStr"/>
       <c r="U286" t="inlineStr"/>
+      <c r="V286" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -20252,6 +21682,11 @@
       <c r="S287" t="inlineStr"/>
       <c r="T287" t="inlineStr"/>
       <c r="U287" t="inlineStr"/>
+      <c r="V287" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -20317,6 +21752,11 @@
       <c r="S288" t="inlineStr"/>
       <c r="T288" t="inlineStr"/>
       <c r="U288" t="inlineStr"/>
+      <c r="V288" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -20382,6 +21822,11 @@
       <c r="S289" t="inlineStr"/>
       <c r="T289" t="inlineStr"/>
       <c r="U289" t="inlineStr"/>
+      <c r="V289" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -20439,6 +21884,11 @@
       <c r="S290" t="inlineStr"/>
       <c r="T290" t="inlineStr"/>
       <c r="U290" t="inlineStr"/>
+      <c r="V290" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -20504,6 +21954,11 @@
           <t>SELF_UNIT</t>
         </is>
       </c>
+      <c r="V291" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -20573,6 +22028,11 @@
       <c r="S292" t="inlineStr"/>
       <c r="T292" t="inlineStr"/>
       <c r="U292" t="inlineStr"/>
+      <c r="V292" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -20650,6 +22110,11 @@
       <c r="S293" t="inlineStr"/>
       <c r="T293" t="inlineStr"/>
       <c r="U293" t="inlineStr"/>
+      <c r="V293" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -20725,6 +22190,11 @@
       <c r="U294" t="inlineStr">
         <is>
           <t>ENEMY_UNIT</t>
+        </is>
+      </c>
+      <c r="V294" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -20792,6 +22262,11 @@
       <c r="S295" t="inlineStr"/>
       <c r="T295" t="inlineStr"/>
       <c r="U295" t="inlineStr"/>
+      <c r="V295" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -20857,6 +22332,11 @@
           <t>SELF_UNIT</t>
         </is>
       </c>
+      <c r="V296" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -20928,6 +22408,11 @@
       <c r="U297" t="inlineStr">
         <is>
           <t>FRIENDLY_UNIT</t>
+        </is>
+      </c>
+      <c r="V297" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -20995,6 +22480,11 @@
       <c r="S298" t="inlineStr"/>
       <c r="T298" t="inlineStr"/>
       <c r="U298" t="inlineStr"/>
+      <c r="V298" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -21060,6 +22550,11 @@
       <c r="S299" t="inlineStr"/>
       <c r="T299" t="inlineStr"/>
       <c r="U299" t="inlineStr"/>
+      <c r="V299" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -21133,6 +22628,11 @@
           <t>FRIENDLY_UNIT</t>
         </is>
       </c>
+      <c r="V300" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -21196,6 +22696,11 @@
       <c r="U301" t="inlineStr">
         <is>
           <t>SELF_UNIT</t>
+        </is>
+      </c>
+      <c r="V301" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -21263,6 +22768,11 @@
       <c r="S302" t="inlineStr"/>
       <c r="T302" t="inlineStr"/>
       <c r="U302" t="inlineStr"/>
+      <c r="V302" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -21340,6 +22850,11 @@
           <t>SELF_UNIT</t>
         </is>
       </c>
+      <c r="V303" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -21417,6 +22932,11 @@
       <c r="S304" t="inlineStr"/>
       <c r="T304" t="inlineStr"/>
       <c r="U304" t="inlineStr"/>
+      <c r="V304" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -21480,6 +23000,11 @@
       <c r="U305" t="inlineStr">
         <is>
           <t>SELF_UNIT</t>
+        </is>
+      </c>
+      <c r="V305" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -21547,6 +23072,11 @@
       <c r="S306" t="inlineStr"/>
       <c r="T306" t="inlineStr"/>
       <c r="U306" t="inlineStr"/>
+      <c r="V306" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -21624,6 +23154,11 @@
           <t>SELF_UNIT</t>
         </is>
       </c>
+      <c r="V307" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -21697,6 +23232,11 @@
       <c r="S308" t="inlineStr"/>
       <c r="T308" t="inlineStr"/>
       <c r="U308" t="inlineStr"/>
+      <c r="V308" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -21770,6 +23310,11 @@
       <c r="S309" t="inlineStr"/>
       <c r="T309" t="inlineStr"/>
       <c r="U309" t="inlineStr"/>
+      <c r="V309" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -21839,6 +23384,11 @@
       <c r="S310" t="inlineStr"/>
       <c r="T310" t="inlineStr"/>
       <c r="U310" t="inlineStr"/>
+      <c r="V310" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -21908,6 +23458,11 @@
       <c r="S311" t="inlineStr"/>
       <c r="T311" t="inlineStr"/>
       <c r="U311" t="inlineStr"/>
+      <c r="V311" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -21973,6 +23528,11 @@
       <c r="S312" t="inlineStr"/>
       <c r="T312" t="inlineStr"/>
       <c r="U312" t="inlineStr"/>
+      <c r="V312" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -22038,6 +23598,11 @@
       <c r="S313" t="inlineStr"/>
       <c r="T313" t="inlineStr"/>
       <c r="U313" t="inlineStr"/>
+      <c r="V313" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -22109,6 +23674,11 @@
       <c r="U314" t="inlineStr">
         <is>
           <t>FRIENDLY_UNIT</t>
+        </is>
+      </c>
+      <c r="V314" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -22176,6 +23746,11 @@
       <c r="S315" t="inlineStr"/>
       <c r="T315" t="inlineStr"/>
       <c r="U315" t="inlineStr"/>
+      <c r="V315" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -22249,6 +23824,11 @@
       <c r="S316" t="inlineStr"/>
       <c r="T316" t="inlineStr"/>
       <c r="U316" t="inlineStr"/>
+      <c r="V316" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -22332,6 +23912,11 @@
       <c r="U317" t="inlineStr">
         <is>
           <t>SELF</t>
+        </is>
+      </c>
+      <c r="V317" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -22399,6 +23984,11 @@
           <t>SELF_UNIT</t>
         </is>
       </c>
+      <c r="V318" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -22462,6 +24052,11 @@
       <c r="U319" t="inlineStr">
         <is>
           <t>SELF_UNIT</t>
+        </is>
+      </c>
+      <c r="V319" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -22529,6 +24124,11 @@
       <c r="S320" t="inlineStr"/>
       <c r="T320" t="inlineStr"/>
       <c r="U320" t="inlineStr"/>
+      <c r="V320" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -22594,6 +24194,11 @@
       <c r="S321" t="inlineStr"/>
       <c r="T321" t="inlineStr"/>
       <c r="U321" t="inlineStr"/>
+      <c r="V321" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -22659,6 +24264,11 @@
       <c r="S322" t="inlineStr"/>
       <c r="T322" t="inlineStr"/>
       <c r="U322" t="inlineStr"/>
+      <c r="V322" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -22730,6 +24340,11 @@
       <c r="U323" t="inlineStr">
         <is>
           <t>FRIENDLY_UNIT</t>
+        </is>
+      </c>
+      <c r="V323" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -22797,6 +24412,11 @@
       <c r="S324" t="inlineStr"/>
       <c r="T324" t="inlineStr"/>
       <c r="U324" t="inlineStr"/>
+      <c r="V324" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -22862,6 +24482,11 @@
       <c r="S325" t="inlineStr"/>
       <c r="T325" t="inlineStr"/>
       <c r="U325" t="inlineStr"/>
+      <c r="V325" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -22931,6 +24556,11 @@
       <c r="S326" t="inlineStr"/>
       <c r="T326" t="inlineStr"/>
       <c r="U326" t="inlineStr"/>
+      <c r="V326" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -23010,6 +24640,11 @@
       <c r="U327" t="inlineStr">
         <is>
           <t>SELF_UNIT</t>
+        </is>
+      </c>
+      <c r="V327" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -23081,6 +24716,11 @@
       <c r="S328" t="inlineStr"/>
       <c r="T328" t="inlineStr"/>
       <c r="U328" t="inlineStr"/>
+      <c r="V328" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -23162,6 +24802,11 @@
           <t>SELF_UNIT</t>
         </is>
       </c>
+      <c r="V329" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -23235,6 +24880,11 @@
       <c r="S330" t="inlineStr"/>
       <c r="T330" t="inlineStr"/>
       <c r="U330" t="inlineStr"/>
+      <c r="V330" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -23308,6 +24958,11 @@
       <c r="S331" t="inlineStr"/>
       <c r="T331" t="inlineStr"/>
       <c r="U331" t="inlineStr"/>
+      <c r="V331" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -23385,6 +25040,11 @@
       <c r="S332" t="inlineStr"/>
       <c r="T332" t="inlineStr"/>
       <c r="U332" t="inlineStr"/>
+      <c r="V332" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -23466,6 +25126,11 @@
           <t>SELF_UNIT</t>
         </is>
       </c>
+      <c r="V333" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -23539,6 +25204,11 @@
       <c r="S334" t="inlineStr"/>
       <c r="T334" t="inlineStr"/>
       <c r="U334" t="inlineStr"/>
+      <c r="V334" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -23612,6 +25282,11 @@
       <c r="S335" t="inlineStr"/>
       <c r="T335" t="inlineStr"/>
       <c r="U335" t="inlineStr"/>
+      <c r="V335" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -23677,6 +25352,11 @@
       <c r="S336" t="inlineStr"/>
       <c r="T336" t="inlineStr"/>
       <c r="U336" t="inlineStr"/>
+      <c r="V336" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -23742,6 +25422,11 @@
       <c r="S337" t="inlineStr"/>
       <c r="T337" t="inlineStr"/>
       <c r="U337" t="inlineStr"/>
+      <c r="V337" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -23803,6 +25488,11 @@
       <c r="S338" t="inlineStr"/>
       <c r="T338" t="inlineStr"/>
       <c r="U338" t="inlineStr"/>
+      <c r="V338" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -23876,6 +25566,11 @@
       <c r="S339" t="inlineStr"/>
       <c r="T339" t="inlineStr"/>
       <c r="U339" t="inlineStr"/>
+      <c r="V339" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -23949,6 +25644,11 @@
           <t>FRIENDLY_UNIT</t>
         </is>
       </c>
+      <c r="V340" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -24022,6 +25722,11 @@
       <c r="S341" t="inlineStr"/>
       <c r="T341" t="inlineStr"/>
       <c r="U341" t="inlineStr"/>
+      <c r="V341" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -24095,6 +25800,11 @@
           <t>FRIENDLY_UNIT</t>
         </is>
       </c>
+      <c r="V342" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -24166,6 +25876,11 @@
       <c r="U343" t="inlineStr">
         <is>
           <t>FRIENDLY_UNIT</t>
+        </is>
+      </c>
+      <c r="V343" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -24233,6 +25948,11 @@
       <c r="S344" t="inlineStr"/>
       <c r="T344" t="inlineStr"/>
       <c r="U344" t="inlineStr"/>
+      <c r="V344" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -24306,6 +26026,11 @@
           <t>FRIENDLY_UNIT</t>
         </is>
       </c>
+      <c r="V345" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -24377,6 +26102,11 @@
       <c r="U346" t="inlineStr">
         <is>
           <t>FRIENDLY_UNIT</t>
+        </is>
+      </c>
+      <c r="V346" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -24444,6 +26174,11 @@
       <c r="S347" t="inlineStr"/>
       <c r="T347" t="inlineStr"/>
       <c r="U347" t="inlineStr"/>
+      <c r="V347" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -24509,6 +26244,11 @@
       <c r="S348" t="inlineStr"/>
       <c r="T348" t="inlineStr"/>
       <c r="U348" t="inlineStr"/>
+      <c r="V348" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -24580,6 +26320,11 @@
       <c r="U349" t="inlineStr">
         <is>
           <t>FRIENDLY_UNIT</t>
+        </is>
+      </c>
+      <c r="V349" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -24647,6 +26392,11 @@
       <c r="S350" t="inlineStr"/>
       <c r="T350" t="inlineStr"/>
       <c r="U350" t="inlineStr"/>
+      <c r="V350" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -24712,6 +26462,11 @@
       <c r="S351" t="inlineStr"/>
       <c r="T351" t="inlineStr"/>
       <c r="U351" t="inlineStr"/>
+      <c r="V351" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -24785,6 +26540,11 @@
       <c r="S352" t="inlineStr"/>
       <c r="T352" t="inlineStr"/>
       <c r="U352" t="inlineStr"/>
+      <c r="V352" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -24850,6 +26610,11 @@
       <c r="S353" t="inlineStr"/>
       <c r="T353" t="inlineStr"/>
       <c r="U353" t="inlineStr"/>
+      <c r="V353" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -24923,6 +26688,11 @@
       <c r="S354" t="inlineStr"/>
       <c r="T354" t="inlineStr"/>
       <c r="U354" t="inlineStr"/>
+      <c r="V354" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -24976,6 +26746,11 @@
       <c r="S355" t="inlineStr"/>
       <c r="T355" t="inlineStr"/>
       <c r="U355" t="inlineStr"/>
+      <c r="V355" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -25029,6 +26804,11 @@
       <c r="S356" t="inlineStr"/>
       <c r="T356" t="inlineStr"/>
       <c r="U356" t="inlineStr"/>
+      <c r="V356" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -25094,6 +26874,11 @@
           <t>SELF_UNIT</t>
         </is>
       </c>
+      <c r="V357" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -25165,6 +26950,11 @@
       <c r="U358" t="inlineStr">
         <is>
           <t>ENEMY_UNIT</t>
+        </is>
+      </c>
+      <c r="V358" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -25232,6 +27022,11 @@
       <c r="S359" t="inlineStr"/>
       <c r="T359" t="inlineStr"/>
       <c r="U359" t="inlineStr"/>
+      <c r="V359" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -25301,6 +27096,11 @@
       <c r="S360" t="inlineStr"/>
       <c r="T360" t="inlineStr"/>
       <c r="U360" t="inlineStr"/>
+      <c r="V360" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -25366,6 +27166,11 @@
           <t>SELF_UNIT</t>
         </is>
       </c>
+      <c r="V361" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -25429,6 +27234,11 @@
       <c r="U362" t="inlineStr">
         <is>
           <t>SELF_UNIT</t>
+        </is>
+      </c>
+      <c r="V362" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -25496,6 +27306,11 @@
           <t>SELF_UNIT</t>
         </is>
       </c>
+      <c r="V363" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -25571,6 +27386,11 @@
       <c r="U364" t="inlineStr">
         <is>
           <t>FRIENDLY_UNIT</t>
+        </is>
+      </c>
+      <c r="V364" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -25646,6 +27466,11 @@
       <c r="S365" t="inlineStr"/>
       <c r="T365" t="inlineStr"/>
       <c r="U365" t="inlineStr"/>
+      <c r="V365" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -25703,6 +27528,11 @@
       <c r="S366" t="inlineStr"/>
       <c r="T366" t="inlineStr"/>
       <c r="U366" t="inlineStr"/>
+      <c r="V366" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -25768,6 +27598,11 @@
           <t>SELF_UNIT</t>
         </is>
       </c>
+      <c r="V367" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -25841,6 +27676,11 @@
       <c r="S368" t="inlineStr"/>
       <c r="T368" t="inlineStr"/>
       <c r="U368" t="inlineStr"/>
+      <c r="V368" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -25912,6 +27752,11 @@
       <c r="U369" t="inlineStr">
         <is>
           <t>FRIENDLY_UNIT</t>
+        </is>
+      </c>
+      <c r="V369" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -25979,6 +27824,11 @@
       <c r="S370" t="inlineStr"/>
       <c r="T370" t="inlineStr"/>
       <c r="U370" t="inlineStr"/>
+      <c r="V370" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -26044,6 +27894,11 @@
           <t>SELF_UNIT</t>
         </is>
       </c>
+      <c r="V371" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -26097,6 +27952,11 @@
       <c r="S372" t="inlineStr"/>
       <c r="T372" t="inlineStr"/>
       <c r="U372" t="inlineStr"/>
+      <c r="V372" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -26154,6 +28014,11 @@
       <c r="S373" t="inlineStr"/>
       <c r="T373" t="inlineStr"/>
       <c r="U373" t="inlineStr"/>
+      <c r="V373" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -26219,6 +28084,11 @@
       <c r="S374" t="inlineStr"/>
       <c r="T374" t="inlineStr"/>
       <c r="U374" t="inlineStr"/>
+      <c r="V374" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -26284,6 +28154,11 @@
           <t>SELF_UNIT</t>
         </is>
       </c>
+      <c r="V375" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -26357,6 +28232,11 @@
       <c r="S376" t="inlineStr"/>
       <c r="T376" t="inlineStr"/>
       <c r="U376" t="inlineStr"/>
+      <c r="V376" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -26422,6 +28302,11 @@
           <t>SELF_UNIT</t>
         </is>
       </c>
+      <c r="V377" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -26495,6 +28380,11 @@
           <t>FRIENDLY_UNIT</t>
         </is>
       </c>
+      <c r="V378" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -26556,6 +28446,11 @@
       <c r="S379" t="inlineStr"/>
       <c r="T379" t="inlineStr"/>
       <c r="U379" t="inlineStr"/>
+      <c r="V379" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -26625,6 +28520,11 @@
       <c r="S380" t="inlineStr"/>
       <c r="T380" t="inlineStr"/>
       <c r="U380" t="inlineStr"/>
+      <c r="V380" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -26706,6 +28606,11 @@
       <c r="S381" t="inlineStr"/>
       <c r="T381" t="inlineStr"/>
       <c r="U381" t="inlineStr"/>
+      <c r="V381" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -26787,6 +28692,11 @@
           <t>SELF_UNIT</t>
         </is>
       </c>
+      <c r="V382" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -26860,6 +28770,11 @@
           <t>ENEMY_UNIT</t>
         </is>
       </c>
+      <c r="V383" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -26925,6 +28840,11 @@
           <t>SELF_UNIT</t>
         </is>
       </c>
+      <c r="V384" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -27002,6 +28922,11 @@
           <t>ENEMY_UNIT</t>
         </is>
       </c>
+      <c r="V385" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -27065,6 +28990,11 @@
       <c r="U386" t="inlineStr">
         <is>
           <t>SELF_UNIT</t>
+        </is>
+      </c>
+      <c r="V386" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -27136,6 +29066,11 @@
       <c r="S387" t="inlineStr"/>
       <c r="T387" t="inlineStr"/>
       <c r="U387" t="inlineStr"/>
+      <c r="V387" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -27201,6 +29136,11 @@
           <t>SELF_UNIT</t>
         </is>
       </c>
+      <c r="V388" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -27262,6 +29202,11 @@
       <c r="S389" t="inlineStr"/>
       <c r="T389" t="inlineStr"/>
       <c r="U389" t="inlineStr"/>
+      <c r="V389" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -27333,6 +29278,11 @@
       <c r="U390" t="inlineStr">
         <is>
           <t>FRIENDLY_UNIT</t>
+        </is>
+      </c>
+      <c r="V390" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -27400,6 +29350,11 @@
       <c r="S391" t="inlineStr"/>
       <c r="T391" t="inlineStr"/>
       <c r="U391" t="inlineStr"/>
+      <c r="V391" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -27465,6 +29420,11 @@
       <c r="S392" t="inlineStr"/>
       <c r="T392" t="inlineStr"/>
       <c r="U392" t="inlineStr"/>
+      <c r="V392" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -27534,6 +29494,11 @@
       <c r="S393" t="inlineStr"/>
       <c r="T393" t="inlineStr"/>
       <c r="U393" t="inlineStr"/>
+      <c r="V393" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -27615,6 +29580,11 @@
           <t>SELF_UNIT</t>
         </is>
       </c>
+      <c r="V394" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -27672,6 +29642,11 @@
       <c r="S395" t="inlineStr"/>
       <c r="T395" t="inlineStr"/>
       <c r="U395" t="inlineStr"/>
+      <c r="V395" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -27737,6 +29712,11 @@
           <t>SELF_UNIT</t>
         </is>
       </c>
+      <c r="V396" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -27810,6 +29790,11 @@
       <c r="S397" t="inlineStr"/>
       <c r="T397" t="inlineStr"/>
       <c r="U397" t="inlineStr"/>
+      <c r="V397" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -27883,6 +29868,11 @@
       <c r="S398" t="inlineStr"/>
       <c r="T398" t="inlineStr"/>
       <c r="U398" t="inlineStr"/>
+      <c r="V398" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -27946,6 +29936,11 @@
       <c r="U399" t="inlineStr">
         <is>
           <t>SELF_UNIT</t>
+        </is>
+      </c>
+      <c r="V399" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -28013,6 +30008,11 @@
       <c r="S400" t="inlineStr"/>
       <c r="T400" t="inlineStr"/>
       <c r="U400" t="inlineStr"/>
+      <c r="V400" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -28078,6 +30078,11 @@
       <c r="S401" t="inlineStr"/>
       <c r="T401" t="inlineStr"/>
       <c r="U401" t="inlineStr"/>
+      <c r="V401" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -28143,6 +30148,11 @@
       <c r="S402" t="inlineStr"/>
       <c r="T402" t="inlineStr"/>
       <c r="U402" t="inlineStr"/>
+      <c r="V402" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -28204,6 +30214,11 @@
       <c r="S403" t="inlineStr"/>
       <c r="T403" t="inlineStr"/>
       <c r="U403" t="inlineStr"/>
+      <c r="V403" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -28277,6 +30292,11 @@
       <c r="S404" t="inlineStr"/>
       <c r="T404" t="inlineStr"/>
       <c r="U404" t="inlineStr"/>
+      <c r="V404" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -28348,6 +30368,11 @@
       <c r="U405" t="inlineStr">
         <is>
           <t>FRIENDLY_UNIT</t>
+        </is>
+      </c>
+      <c r="V405" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -28415,6 +30440,11 @@
       <c r="S406" t="inlineStr"/>
       <c r="T406" t="inlineStr"/>
       <c r="U406" t="inlineStr"/>
+      <c r="V406" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -28488,6 +30518,11 @@
           <t>FRIENDLY_UNIT</t>
         </is>
       </c>
+      <c r="V407" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -28561,6 +30596,11 @@
       <c r="S408" t="inlineStr"/>
       <c r="T408" t="inlineStr"/>
       <c r="U408" t="inlineStr"/>
+      <c r="V408" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -28626,6 +30666,11 @@
       <c r="S409" t="inlineStr"/>
       <c r="T409" t="inlineStr"/>
       <c r="U409" t="inlineStr"/>
+      <c r="V409" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -28691,6 +30736,11 @@
       <c r="S410" t="inlineStr"/>
       <c r="T410" t="inlineStr"/>
       <c r="U410" t="inlineStr"/>
+      <c r="V410" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -28772,6 +30822,11 @@
           <t>SELF_UNIT</t>
         </is>
       </c>
+      <c r="V411" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -28845,6 +30900,11 @@
           <t>ENEMY_UNIT</t>
         </is>
       </c>
+      <c r="V412" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -28918,6 +30978,11 @@
       <c r="S413" t="inlineStr"/>
       <c r="T413" t="inlineStr"/>
       <c r="U413" t="inlineStr"/>
+      <c r="V413" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -28991,6 +31056,11 @@
           <t>ENEMY_UNIT</t>
         </is>
       </c>
+      <c r="V414" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -29056,6 +31126,11 @@
           <t>SELF_UNIT</t>
         </is>
       </c>
+      <c r="V415" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -29119,6 +31194,11 @@
       <c r="U416" t="inlineStr">
         <is>
           <t>SELF_UNIT</t>
+        </is>
+      </c>
+      <c r="V416" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -29190,6 +31270,11 @@
       <c r="S417" t="inlineStr"/>
       <c r="T417" t="inlineStr"/>
       <c r="U417" t="inlineStr"/>
+      <c r="V417" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -29263,6 +31348,11 @@
           <t>FRIENDLY_UNIT</t>
         </is>
       </c>
+      <c r="V418" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -29332,6 +31422,11 @@
       <c r="S419" t="inlineStr"/>
       <c r="T419" t="inlineStr"/>
       <c r="U419" t="inlineStr"/>
+      <c r="V419" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -29397,6 +31492,11 @@
       <c r="S420" t="inlineStr"/>
       <c r="T420" t="inlineStr"/>
       <c r="U420" t="inlineStr"/>
+      <c r="V420" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -29462,6 +31562,11 @@
       <c r="S421" t="inlineStr"/>
       <c r="T421" t="inlineStr"/>
       <c r="U421" t="inlineStr"/>
+      <c r="V421" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -29535,6 +31640,11 @@
       <c r="S422" t="inlineStr"/>
       <c r="T422" t="inlineStr"/>
       <c r="U422" t="inlineStr"/>
+      <c r="V422" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -29606,6 +31716,11 @@
       <c r="U423" t="inlineStr">
         <is>
           <t>ENEMY_UNIT</t>
+        </is>
+      </c>
+      <c r="V423" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -29673,6 +31788,11 @@
       <c r="S424" t="inlineStr"/>
       <c r="T424" t="inlineStr"/>
       <c r="U424" t="inlineStr"/>
+      <c r="V424" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -29738,6 +31858,11 @@
       <c r="S425" t="inlineStr"/>
       <c r="T425" t="inlineStr"/>
       <c r="U425" t="inlineStr"/>
+      <c r="V425" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -29803,6 +31928,11 @@
       <c r="S426" t="inlineStr"/>
       <c r="T426" t="inlineStr"/>
       <c r="U426" t="inlineStr"/>
+      <c r="V426" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -29860,6 +31990,11 @@
       <c r="S427" t="inlineStr"/>
       <c r="T427" t="inlineStr"/>
       <c r="U427" t="inlineStr"/>
+      <c r="V427" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -29937,6 +32072,11 @@
       <c r="S428" t="inlineStr"/>
       <c r="T428" t="inlineStr"/>
       <c r="U428" t="inlineStr"/>
+      <c r="V428" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -30006,6 +32146,11 @@
       <c r="S429" t="inlineStr"/>
       <c r="T429" t="inlineStr"/>
       <c r="U429" t="inlineStr"/>
+      <c r="V429" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -30071,6 +32216,11 @@
           <t>SELF_UNIT</t>
         </is>
       </c>
+      <c r="V430" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -30124,6 +32274,11 @@
       <c r="S431" t="inlineStr"/>
       <c r="T431" t="inlineStr"/>
       <c r="U431" t="inlineStr"/>
+      <c r="V431" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -30181,6 +32336,11 @@
       <c r="S432" t="inlineStr"/>
       <c r="T432" t="inlineStr"/>
       <c r="U432" t="inlineStr"/>
+      <c r="V432" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -30252,6 +32412,11 @@
       <c r="U433" t="inlineStr">
         <is>
           <t>FRIENDLY_UNIT</t>
+        </is>
+      </c>
+      <c r="V433" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -30327,6 +32492,11 @@
           <t>FRIENDLY_UNIT</t>
         </is>
       </c>
+      <c r="V434" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -30384,6 +32554,11 @@
       <c r="S435" t="inlineStr"/>
       <c r="T435" t="inlineStr"/>
       <c r="U435" t="inlineStr"/>
+      <c r="V435" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -30449,6 +32624,11 @@
       <c r="S436" t="inlineStr"/>
       <c r="T436" t="inlineStr"/>
       <c r="U436" t="inlineStr"/>
+      <c r="V436" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -30506,6 +32686,11 @@
       <c r="S437" t="inlineStr"/>
       <c r="T437" t="inlineStr"/>
       <c r="U437" t="inlineStr"/>
+      <c r="V437" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -30571,6 +32756,11 @@
           <t>SELF_UNIT</t>
         </is>
       </c>
+      <c r="V438" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -30646,6 +32836,11 @@
       <c r="U439" t="inlineStr">
         <is>
           <t>FRIENDLY_UNIT</t>
+        </is>
+      </c>
+      <c r="V439" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -30713,6 +32908,11 @@
           <t>SELF_UNIT</t>
         </is>
       </c>
+      <c r="V440" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -30786,6 +32986,11 @@
           <t>FRIENDLY_UNIT</t>
         </is>
       </c>
+      <c r="V441" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -30859,6 +33064,11 @@
       <c r="S442" t="inlineStr"/>
       <c r="T442" t="inlineStr"/>
       <c r="U442" t="inlineStr"/>
+      <c r="V442" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -30932,6 +33142,11 @@
       <c r="S443" t="inlineStr"/>
       <c r="T443" t="inlineStr"/>
       <c r="U443" t="inlineStr"/>
+      <c r="V443" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -31005,6 +33220,11 @@
       <c r="S444" t="inlineStr"/>
       <c r="T444" t="inlineStr"/>
       <c r="U444" t="inlineStr"/>
+      <c r="V444" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -31070,6 +33290,11 @@
       <c r="S445" t="inlineStr"/>
       <c r="T445" t="inlineStr"/>
       <c r="U445" t="inlineStr"/>
+      <c r="V445" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -31143,6 +33368,11 @@
       <c r="S446" t="inlineStr"/>
       <c r="T446" t="inlineStr"/>
       <c r="U446" t="inlineStr"/>
+      <c r="V446" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -31212,6 +33442,11 @@
       <c r="S447" t="inlineStr"/>
       <c r="T447" t="inlineStr"/>
       <c r="U447" t="inlineStr"/>
+      <c r="V447" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -31293,6 +33528,11 @@
           <t>SELF_UNIT</t>
         </is>
       </c>
+      <c r="V448" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -31362,6 +33602,11 @@
       <c r="S449" t="inlineStr"/>
       <c r="T449" t="inlineStr"/>
       <c r="U449" t="inlineStr"/>
+      <c r="V449" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -31427,6 +33672,11 @@
           <t>SELF_UNIT</t>
         </is>
       </c>
+      <c r="V450" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -31496,6 +33746,11 @@
       <c r="S451" t="inlineStr"/>
       <c r="T451" t="inlineStr"/>
       <c r="U451" t="inlineStr"/>
+      <c r="V451" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -31573,6 +33828,11 @@
       <c r="S452" t="inlineStr"/>
       <c r="T452" t="inlineStr"/>
       <c r="U452" t="inlineStr"/>
+      <c r="V452" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -31626,6 +33886,11 @@
       <c r="S453" t="inlineStr"/>
       <c r="T453" t="inlineStr"/>
       <c r="U453" t="inlineStr"/>
+      <c r="V453" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -31691,6 +33956,11 @@
           <t>SELF_UNIT</t>
         </is>
       </c>
+      <c r="V454" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -31762,6 +34032,11 @@
       <c r="U455" t="inlineStr">
         <is>
           <t>FRIENDLY_UNIT</t>
+        </is>
+      </c>
+      <c r="V455" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -31829,6 +34104,11 @@
       <c r="S456" t="inlineStr"/>
       <c r="T456" t="inlineStr"/>
       <c r="U456" t="inlineStr"/>
+      <c r="V456" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -31898,6 +34178,11 @@
       <c r="S457" t="inlineStr"/>
       <c r="T457" t="inlineStr"/>
       <c r="U457" t="inlineStr"/>
+      <c r="V457" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -31967,6 +34252,11 @@
       <c r="S458" t="inlineStr"/>
       <c r="T458" t="inlineStr"/>
       <c r="U458" t="inlineStr"/>
+      <c r="V458" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -32032,6 +34322,11 @@
           <t>SELF_UNIT</t>
         </is>
       </c>
+      <c r="V459" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -32105,6 +34400,11 @@
       <c r="S460" t="inlineStr"/>
       <c r="T460" t="inlineStr"/>
       <c r="U460" t="inlineStr"/>
+      <c r="V460" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -32174,6 +34474,11 @@
       <c r="S461" t="inlineStr"/>
       <c r="T461" t="inlineStr"/>
       <c r="U461" t="inlineStr"/>
+      <c r="V461" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -32227,6 +34532,11 @@
       <c r="S462" t="inlineStr"/>
       <c r="T462" t="inlineStr"/>
       <c r="U462" t="inlineStr"/>
+      <c r="V462" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -32292,6 +34602,11 @@
           <t>SELF_UNIT</t>
         </is>
       </c>
+      <c r="V463" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -32353,6 +34668,11 @@
       <c r="S464" t="inlineStr"/>
       <c r="T464" t="inlineStr"/>
       <c r="U464" t="inlineStr"/>
+      <c r="V464" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -32424,6 +34744,11 @@
       <c r="U465" t="inlineStr">
         <is>
           <t>ENEMY_UNIT</t>
+        </is>
+      </c>
+      <c r="V465" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -32499,6 +34824,11 @@
           <t>ENEMY_UNIT</t>
         </is>
       </c>
+      <c r="V466" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -32568,6 +34898,11 @@
       <c r="S467" t="inlineStr"/>
       <c r="T467" t="inlineStr"/>
       <c r="U467" t="inlineStr"/>
+      <c r="V467" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -32631,6 +34966,11 @@
       <c r="U468" t="inlineStr">
         <is>
           <t>SELF_UNIT</t>
+        </is>
+      </c>
+      <c r="V468" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -32698,6 +35038,11 @@
       <c r="S469" t="inlineStr"/>
       <c r="T469" t="inlineStr"/>
       <c r="U469" t="inlineStr"/>
+      <c r="V469" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -32763,6 +35108,11 @@
       <c r="S470" t="inlineStr"/>
       <c r="T470" t="inlineStr"/>
       <c r="U470" t="inlineStr"/>
+      <c r="V470" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -32836,6 +35186,11 @@
           <t>ENEMY_UNIT</t>
         </is>
       </c>
+      <c r="V471" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -32909,6 +35264,11 @@
           <t>ENEMY_UNIT</t>
         </is>
       </c>
+      <c r="V472" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -32982,6 +35342,11 @@
       <c r="S473" t="inlineStr"/>
       <c r="T473" t="inlineStr"/>
       <c r="U473" t="inlineStr"/>
+      <c r="V473" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -33051,6 +35416,11 @@
       <c r="S474" t="inlineStr"/>
       <c r="T474" t="inlineStr"/>
       <c r="U474" t="inlineStr"/>
+      <c r="V474" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -33116,6 +35486,11 @@
           <t>SELF_UNIT</t>
         </is>
       </c>
+      <c r="V475" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -33193,6 +35568,11 @@
           <t>ENEMY_UNIT</t>
         </is>
       </c>
+      <c r="V476" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -33262,6 +35642,11 @@
       <c r="S477" t="inlineStr"/>
       <c r="T477" t="inlineStr"/>
       <c r="U477" t="inlineStr"/>
+      <c r="V477" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -33327,6 +35712,11 @@
           <t>SELF_UNIT</t>
         </is>
       </c>
+      <c r="V478" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -33402,6 +35792,11 @@
       <c r="U479" t="inlineStr">
         <is>
           <t>ENEMY_UNIT</t>
+        </is>
+      </c>
+      <c r="V479" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -33469,6 +35864,11 @@
           <t>SELF_UNIT</t>
         </is>
       </c>
+      <c r="V480" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -33534,6 +35934,11 @@
           <t>SELF_UNIT</t>
         </is>
       </c>
+      <c r="V481" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -33609,6 +36014,11 @@
       <c r="U482" t="inlineStr">
         <is>
           <t>ENEMY_UNIT</t>
+        </is>
+      </c>
+      <c r="V482" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -33684,6 +36094,11 @@
           <t>ENEMY_UNIT</t>
         </is>
       </c>
+      <c r="V483" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -33737,6 +36152,11 @@
       <c r="S484" t="inlineStr"/>
       <c r="T484" t="inlineStr"/>
       <c r="U484" t="inlineStr"/>
+      <c r="V484" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -33802,6 +36222,11 @@
           <t>SELF_UNIT</t>
         </is>
       </c>
+      <c r="V485" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -33867,6 +36292,11 @@
           <t>SELF_UNIT</t>
         </is>
       </c>
+      <c r="V486" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -33938,6 +36368,11 @@
       <c r="U487" t="inlineStr">
         <is>
           <t>FRIENDLY_UNIT</t>
+        </is>
+      </c>
+      <c r="V487" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -34005,6 +36440,11 @@
       <c r="S488" t="inlineStr"/>
       <c r="T488" t="inlineStr"/>
       <c r="U488" t="inlineStr"/>
+      <c r="V488" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -34078,6 +36518,11 @@
           <t>FRIENDLY_UNIT</t>
         </is>
       </c>
+      <c r="V489" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -34135,6 +36580,11 @@
       <c r="S490" t="inlineStr"/>
       <c r="T490" t="inlineStr"/>
       <c r="U490" t="inlineStr"/>
+      <c r="V490" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -34202,6 +36652,11 @@
       <c r="U491" t="inlineStr">
         <is>
           <t>SELF</t>
+        </is>
+      </c>
+      <c r="V491" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -34269,6 +36724,11 @@
           <t>SELF_UNIT</t>
         </is>
       </c>
+      <c r="V492" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -34342,6 +36802,11 @@
           <t>FRIENDLY_UNIT</t>
         </is>
       </c>
+      <c r="V493" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -34413,6 +36878,11 @@
       <c r="U494" t="inlineStr">
         <is>
           <t>ENEMY_UNIT</t>
+        </is>
+      </c>
+      <c r="V494" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -34480,6 +36950,11 @@
       <c r="S495" t="inlineStr"/>
       <c r="T495" t="inlineStr"/>
       <c r="U495" t="inlineStr"/>
+      <c r="V495" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -34545,6 +37020,11 @@
       <c r="S496" t="inlineStr"/>
       <c r="T496" t="inlineStr"/>
       <c r="U496" t="inlineStr"/>
+      <c r="V496" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -34614,6 +37094,11 @@
       <c r="S497" t="inlineStr"/>
       <c r="T497" t="inlineStr"/>
       <c r="U497" t="inlineStr"/>
+      <c r="V497" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -34679,6 +37164,11 @@
       <c r="S498" t="inlineStr"/>
       <c r="T498" t="inlineStr"/>
       <c r="U498" t="inlineStr"/>
+      <c r="V498" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -34740,6 +37230,11 @@
       <c r="S499" t="inlineStr"/>
       <c r="T499" t="inlineStr"/>
       <c r="U499" t="inlineStr"/>
+      <c r="V499" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -34813,6 +37308,11 @@
           <t>FRIENDLY_UNIT</t>
         </is>
       </c>
+      <c r="V500" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -34884,6 +37384,11 @@
       <c r="U501" t="inlineStr">
         <is>
           <t>ENEMY_UNIT</t>
+        </is>
+      </c>
+      <c r="V501" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>
@@ -34951,6 +37456,11 @@
       <c r="S502" t="inlineStr"/>
       <c r="T502" t="inlineStr"/>
       <c r="U502" t="inlineStr"/>
+      <c r="V502" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -35016,6 +37526,11 @@
       <c r="S503" t="inlineStr"/>
       <c r="T503" t="inlineStr"/>
       <c r="U503" t="inlineStr"/>
+      <c r="V503" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -35073,6 +37588,11 @@
       <c r="S504" t="inlineStr"/>
       <c r="T504" t="inlineStr"/>
       <c r="U504" t="inlineStr"/>
+      <c r="V504" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -35146,6 +37666,11 @@
       <c r="S505" t="inlineStr"/>
       <c r="T505" t="inlineStr"/>
       <c r="U505" t="inlineStr"/>
+      <c r="V505" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -35211,6 +37736,11 @@
       <c r="S506" t="inlineStr"/>
       <c r="T506" t="inlineStr"/>
       <c r="U506" t="inlineStr"/>
+      <c r="V506" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -35284,6 +37814,11 @@
       <c r="S507" t="inlineStr"/>
       <c r="T507" t="inlineStr"/>
       <c r="U507" t="inlineStr"/>
+      <c r="V507" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -35349,6 +37884,11 @@
       <c r="S508" t="inlineStr"/>
       <c r="T508" t="inlineStr"/>
       <c r="U508" t="inlineStr"/>
+      <c r="V508" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -35422,6 +37962,11 @@
       <c r="S509" t="inlineStr"/>
       <c r="T509" t="inlineStr"/>
       <c r="U509" t="inlineStr"/>
+      <c r="V509" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -35491,6 +38036,11 @@
       <c r="S510" t="inlineStr"/>
       <c r="T510" t="inlineStr"/>
       <c r="U510" t="inlineStr"/>
+      <c r="V510" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -35560,6 +38110,11 @@
       <c r="S511" t="inlineStr"/>
       <c r="T511" t="inlineStr"/>
       <c r="U511" t="inlineStr"/>
+      <c r="V511" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -35629,6 +38184,11 @@
       <c r="S512" t="inlineStr"/>
       <c r="T512" t="inlineStr"/>
       <c r="U512" t="inlineStr"/>
+      <c r="V512" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -35698,6 +38258,11 @@
       <c r="S513" t="inlineStr"/>
       <c r="T513" t="inlineStr"/>
       <c r="U513" t="inlineStr"/>
+      <c r="V513" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -35767,6 +38332,11 @@
       <c r="S514" t="inlineStr"/>
       <c r="T514" t="inlineStr"/>
       <c r="U514" t="inlineStr"/>
+      <c r="V514" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -35840,6 +38410,11 @@
       <c r="S515" t="inlineStr"/>
       <c r="T515" t="inlineStr"/>
       <c r="U515" t="inlineStr"/>
+      <c r="V515" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -35909,6 +38484,11 @@
       <c r="S516" t="inlineStr"/>
       <c r="T516" t="inlineStr"/>
       <c r="U516" t="inlineStr"/>
+      <c r="V516" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -35978,6 +38558,11 @@
       <c r="S517" t="inlineStr"/>
       <c r="T517" t="inlineStr"/>
       <c r="U517" t="inlineStr"/>
+      <c r="V517" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/special_rules_review_matrix.xlsx
+++ b/docs/special_rules_review_matrix.xlsx
@@ -1004,7 +1004,7 @@
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
-          <t>⚠️</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr">
         <is>
-          <t>⚠️</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr">
         <is>
-          <t>⚠️</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr">
         <is>
-          <t>⚠️</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr">
         <is>
-          <t>⚠️</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -2458,7 +2458,7 @@
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr">
         <is>
-          <t>⚠️</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -2532,7 +2532,7 @@
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr">
         <is>
-          <t>⚠️</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -2992,7 +2992,7 @@
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr">
         <is>
-          <t>⚠️</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -3066,7 +3066,7 @@
       <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr">
         <is>
-          <t>⚠️</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       <c r="U35" t="inlineStr"/>
       <c r="V35" t="inlineStr">
         <is>
-          <t>⚠️</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -3292,7 +3292,7 @@
       <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr">
         <is>
-          <t>⚠️</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -4216,7 +4216,7 @@
       <c r="U49" t="inlineStr"/>
       <c r="V49" t="inlineStr">
         <is>
-          <t>⚠️</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -4294,7 +4294,7 @@
       <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr">
         <is>
-          <t>⚠️</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -4372,7 +4372,7 @@
       <c r="U51" t="inlineStr"/>
       <c r="V51" t="inlineStr">
         <is>
-          <t>⚠️</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -4602,7 +4602,7 @@
       <c r="U54" t="inlineStr"/>
       <c r="V54" t="inlineStr">
         <is>
-          <t>⚠️</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -4676,7 +4676,7 @@
       <c r="U55" t="inlineStr"/>
       <c r="V55" t="inlineStr">
         <is>
-          <t>⚠️</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -4750,7 +4750,7 @@
       <c r="U56" t="inlineStr"/>
       <c r="V56" t="inlineStr">
         <is>
-          <t>⚠️</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -4824,7 +4824,7 @@
       <c r="U57" t="inlineStr"/>
       <c r="V57" t="inlineStr">
         <is>
-          <t>⚠️</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
